--- a/Dashboard Tracker.xlsx
+++ b/Dashboard Tracker.xlsx
@@ -1915,7 +1915,7 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">

--- a/Dashboard Tracker.xlsx
+++ b/Dashboard Tracker.xlsx
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">

--- a/Dashboard Tracker.xlsx
+++ b/Dashboard Tracker.xlsx
@@ -1109,7 +1109,7 @@
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -1229,17 +1229,17 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
           <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>Not Started</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
           <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>Not Started</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">

--- a/Dashboard Tracker.xlsx
+++ b/Dashboard Tracker.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
